--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/MARYLAND_2017.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/MARYLAND_2017.xlsx
@@ -3444,7 +3444,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C172">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C439">
